--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359142</v>
+        <v>122359674</v>
       </c>
       <c r="B2" t="n">
         <v>78645</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583884</v>
+        <v>583906</v>
       </c>
       <c r="R2" t="n">
-        <v>7041633</v>
+        <v>7041535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359201</v>
+        <v>122359142</v>
       </c>
       <c r="B3" t="n">
-        <v>90799</v>
+        <v>78645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,43 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583907</v>
+        <v>583884</v>
       </c>
       <c r="R3" t="n">
-        <v>7041602</v>
+        <v>7041633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122359140</v>
+        <v>122359117</v>
       </c>
       <c r="B4" t="n">
-        <v>55974</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,28 +915,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -957,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583893</v>
+        <v>583895</v>
       </c>
       <c r="R4" t="n">
-        <v>7041630</v>
+        <v>7041636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359117</v>
+        <v>122359168</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1074,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583895</v>
+        <v>583901</v>
       </c>
       <c r="R5" t="n">
-        <v>7041636</v>
+        <v>7041612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,12 +1126,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1263,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122360157</v>
+        <v>122357665</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1299,7 +1291,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1308,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583950</v>
+        <v>583884</v>
       </c>
       <c r="R7" t="n">
-        <v>7041511</v>
+        <v>7041654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122359674</v>
+        <v>122360157</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,34 +1393,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583906</v>
+        <v>583950</v>
       </c>
       <c r="R8" t="n">
-        <v>7041535</v>
+        <v>7041511</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1467,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,22 +1487,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122357665</v>
+        <v>122359201</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>90799</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,27 +1515,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1542,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583884</v>
+        <v>583907</v>
       </c>
       <c r="R9" t="n">
-        <v>7041654</v>
+        <v>7041602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,12 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359168</v>
+        <v>122359140</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>55974</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,24 +1636,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583901</v>
+        <v>583893</v>
       </c>
       <c r="R10" t="n">
-        <v>7041612</v>
+        <v>7041630</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,12 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359674</v>
+        <v>122357665</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583906</v>
+        <v>583884</v>
       </c>
       <c r="R2" t="n">
-        <v>7041535</v>
+        <v>7041654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359142</v>
+        <v>122359140</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>55974</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +813,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583884</v>
+        <v>583893</v>
       </c>
       <c r="R3" t="n">
-        <v>7041633</v>
+        <v>7041630</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +906,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122359117</v>
+        <v>122359142</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +934,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583895</v>
+        <v>583884</v>
       </c>
       <c r="R4" t="n">
-        <v>7041636</v>
+        <v>7041633</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359168</v>
+        <v>122359674</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1046,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583901</v>
+        <v>583906</v>
       </c>
       <c r="R5" t="n">
-        <v>7041612</v>
+        <v>7041535</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359314</v>
+        <v>122359168</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,16 +1158,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1183,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583896</v>
+        <v>583901</v>
       </c>
       <c r="R6" t="n">
-        <v>7041555</v>
+        <v>7041612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122357665</v>
+        <v>122360157</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1291,7 +1300,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1300,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583884</v>
+        <v>583950</v>
       </c>
       <c r="R7" t="n">
-        <v>7041654</v>
+        <v>7041511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122360157</v>
+        <v>122359117</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,16 +1402,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1413,7 +1422,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583950</v>
+        <v>583895</v>
       </c>
       <c r="R8" t="n">
-        <v>7041511</v>
+        <v>7041636</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,12 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,22 +1491,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359201</v>
+        <v>122359314</v>
       </c>
       <c r="B9" t="n">
-        <v>90799</v>
+        <v>57390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,31 +1519,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583907</v>
+        <v>583896</v>
       </c>
       <c r="R9" t="n">
-        <v>7041602</v>
+        <v>7041555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359140</v>
+        <v>122359201</v>
       </c>
       <c r="B10" t="n">
-        <v>55974</v>
+        <v>90809</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583893</v>
+        <v>583907</v>
       </c>
       <c r="R10" t="n">
-        <v>7041630</v>
+        <v>7041602</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122357665</v>
+        <v>122359201</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>90809</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583884</v>
+        <v>583907</v>
       </c>
       <c r="R2" t="n">
-        <v>7041654</v>
+        <v>7041602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359140</v>
+        <v>122359314</v>
       </c>
       <c r="B3" t="n">
-        <v>55974</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,28 +812,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -846,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583893</v>
+        <v>583896</v>
       </c>
       <c r="R3" t="n">
-        <v>7041630</v>
+        <v>7041555</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122359142</v>
+        <v>122357665</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,24 +929,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
@@ -961,7 +961,7 @@
         <v>583884</v>
       </c>
       <c r="R4" t="n">
-        <v>7041633</v>
+        <v>7041654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +1023,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359674</v>
+        <v>122359117</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,34 +1051,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583906</v>
+        <v>583895</v>
       </c>
       <c r="R5" t="n">
-        <v>7041535</v>
+        <v>7041636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359168</v>
+        <v>122359142</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,39 +1168,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583901</v>
+        <v>583884</v>
       </c>
       <c r="R6" t="n">
-        <v>7041612</v>
+        <v>7041633</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,22 +1252,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122360157</v>
+        <v>122359674</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,39 +1280,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583950</v>
+        <v>583906</v>
       </c>
       <c r="R7" t="n">
-        <v>7041511</v>
+        <v>7041535</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,22 +1364,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122359117</v>
+        <v>122359140</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>55974</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,24 +1392,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1431,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583895</v>
+        <v>583893</v>
       </c>
       <c r="R8" t="n">
-        <v>7041636</v>
+        <v>7041630</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,22 +1485,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359314</v>
+        <v>122360157</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,16 +1513,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1539,7 +1533,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1548,10 +1542,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583896</v>
+        <v>583950</v>
       </c>
       <c r="R9" t="n">
-        <v>7041555</v>
+        <v>7041511</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1587,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359201</v>
+        <v>122359168</v>
       </c>
       <c r="B10" t="n">
-        <v>90809</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,31 +1635,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583907</v>
+        <v>583901</v>
       </c>
       <c r="R10" t="n">
-        <v>7041602</v>
+        <v>7041612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1709,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359201</v>
+        <v>122357665</v>
       </c>
       <c r="B2" t="n">
-        <v>90809</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583907</v>
+        <v>583884</v>
       </c>
       <c r="R2" t="n">
-        <v>7041602</v>
+        <v>7041654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359314</v>
+        <v>122359674</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583896</v>
+        <v>583906</v>
       </c>
       <c r="R3" t="n">
-        <v>7041555</v>
+        <v>7041535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122357665</v>
+        <v>122360157</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583884</v>
+        <v>583950</v>
       </c>
       <c r="R4" t="n">
-        <v>7041654</v>
+        <v>7041511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359117</v>
+        <v>122359142</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583895</v>
+        <v>583884</v>
       </c>
       <c r="R5" t="n">
-        <v>7041636</v>
+        <v>7041633</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359142</v>
+        <v>122359201</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>90821</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,34 +1159,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583884</v>
+        <v>583907</v>
       </c>
       <c r="R6" t="n">
-        <v>7041633</v>
+        <v>7041602</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,22 +1252,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122359674</v>
+        <v>122359168</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,34 +1280,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583906</v>
+        <v>583901</v>
       </c>
       <c r="R7" t="n">
-        <v>7041535</v>
+        <v>7041612</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,12 +1374,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1379,7 +1389,7 @@
         <v>122359140</v>
       </c>
       <c r="B8" t="n">
-        <v>55974</v>
+        <v>55979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1497,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122360157</v>
+        <v>122359117</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,16 +1523,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1533,7 +1543,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1542,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583950</v>
+        <v>583895</v>
       </c>
       <c r="R9" t="n">
-        <v>7041511</v>
+        <v>7041636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,12 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,22 +1612,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359168</v>
+        <v>122359314</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>57395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,16 +1640,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583901</v>
+        <v>583896</v>
       </c>
       <c r="R10" t="n">
-        <v>7041612</v>
+        <v>7041555</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,12 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122357665</v>
+        <v>122359201</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>90828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583884</v>
+        <v>583907</v>
       </c>
       <c r="R2" t="n">
-        <v>7041654</v>
+        <v>7041602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359674</v>
+        <v>122359142</v>
       </c>
       <c r="B3" t="n">
         <v>78651</v>
@@ -837,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583906</v>
+        <v>583884</v>
       </c>
       <c r="R3" t="n">
-        <v>7041535</v>
+        <v>7041633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360157</v>
+        <v>122357665</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -945,7 +944,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583950</v>
+        <v>583884</v>
       </c>
       <c r="R4" t="n">
-        <v>7041511</v>
+        <v>7041654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359142</v>
+        <v>122359140</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>55979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1046,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583884</v>
+        <v>583893</v>
       </c>
       <c r="R5" t="n">
-        <v>7041633</v>
+        <v>7041630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1139,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359201</v>
+        <v>122359674</v>
       </c>
       <c r="B6" t="n">
-        <v>90821</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,43 +1167,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583907</v>
+        <v>583906</v>
       </c>
       <c r="R6" t="n">
-        <v>7041602</v>
+        <v>7041535</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,19 +1251,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122359168</v>
+        <v>122360157</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1300,7 +1299,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1309,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583901</v>
+        <v>583950</v>
       </c>
       <c r="R7" t="n">
-        <v>7041612</v>
+        <v>7041511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1353,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1386,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122359140</v>
+        <v>122359117</v>
       </c>
       <c r="B8" t="n">
-        <v>55979</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,28 +1401,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1435,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583893</v>
+        <v>583895</v>
       </c>
       <c r="R8" t="n">
-        <v>7041630</v>
+        <v>7041636</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,19 +1490,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359117</v>
+        <v>122359314</v>
       </c>
       <c r="B9" t="n">
         <v>57395</v>
@@ -1552,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583895</v>
+        <v>583896</v>
       </c>
       <c r="R9" t="n">
-        <v>7041636</v>
+        <v>7041555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,22 +1607,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359314</v>
+        <v>122359168</v>
       </c>
       <c r="B10" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,16 +1635,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583896</v>
+        <v>583901</v>
       </c>
       <c r="R10" t="n">
-        <v>7041555</v>
+        <v>7041612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1709,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359140</v>
+        <v>122359674</v>
       </c>
       <c r="B5" t="n">
-        <v>55979</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,43 +1046,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583893</v>
+        <v>583906</v>
       </c>
       <c r="R5" t="n">
-        <v>7041630</v>
+        <v>7041535</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359674</v>
+        <v>122359140</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>55979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,34 +1158,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583906</v>
+        <v>583893</v>
       </c>
       <c r="R6" t="n">
-        <v>7041535</v>
+        <v>7041630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,12 +1251,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359201</v>
+        <v>122359142</v>
       </c>
       <c r="B2" t="n">
-        <v>90828</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583907</v>
+        <v>583884</v>
       </c>
       <c r="R2" t="n">
-        <v>7041602</v>
+        <v>7041633</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359142</v>
+        <v>122359674</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,11 +800,6 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -836,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583884</v>
+        <v>583906</v>
       </c>
       <c r="R3" t="n">
-        <v>7041633</v>
+        <v>7041535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122357665</v>
+        <v>122360157</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -926,11 +907,6 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -944,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583884</v>
+        <v>583950</v>
       </c>
       <c r="R4" t="n">
-        <v>7041654</v>
+        <v>7041511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359674</v>
+        <v>122359117</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,34 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583906</v>
+        <v>583895</v>
       </c>
       <c r="R5" t="n">
-        <v>7041535</v>
+        <v>7041636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359140</v>
+        <v>122359314</v>
       </c>
       <c r="B6" t="n">
-        <v>55979</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,28 +1134,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Skogshare</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1191,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583893</v>
+        <v>583896</v>
       </c>
       <c r="R6" t="n">
-        <v>7041630</v>
+        <v>7041555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122360157</v>
+        <v>122359201</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>90833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,27 +1246,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1308,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583950</v>
+        <v>583907</v>
       </c>
       <c r="R7" t="n">
-        <v>7041511</v>
+        <v>7041602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122359117</v>
+        <v>122357665</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,16 +1362,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1430,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583895</v>
+        <v>583884</v>
       </c>
       <c r="R8" t="n">
-        <v>7041636</v>
+        <v>7041654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1431,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,22 +1451,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359314</v>
+        <v>122359168</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,16 +1479,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1547,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583896</v>
+        <v>583901</v>
       </c>
       <c r="R9" t="n">
-        <v>7041555</v>
+        <v>7041612</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1548,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359168</v>
+        <v>122359140</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>55979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,24 +1596,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>206004</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1664,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583901</v>
+        <v>583893</v>
       </c>
       <c r="R10" t="n">
-        <v>7041612</v>
+        <v>7041630</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,12 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359142</v>
+        <v>122360157</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583884</v>
+        <v>583950</v>
       </c>
       <c r="R2" t="n">
-        <v>7041633</v>
+        <v>7041511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359674</v>
+        <v>122359201</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>90846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,29 +813,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583906</v>
+        <v>583907</v>
       </c>
       <c r="R3" t="n">
-        <v>7041535</v>
+        <v>7041602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +906,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360157</v>
+        <v>122359314</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,11 +934,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -920,7 +954,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583950</v>
+        <v>583896</v>
       </c>
       <c r="R4" t="n">
-        <v>7041511</v>
+        <v>7041555</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359117</v>
+        <v>122359674</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,34 +1051,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583895</v>
+        <v>583906</v>
       </c>
       <c r="R5" t="n">
-        <v>7041636</v>
+        <v>7041535</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359314</v>
+        <v>122359140</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>55983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,19 +1163,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>206004</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1158,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583896</v>
+        <v>583893</v>
       </c>
       <c r="R6" t="n">
-        <v>7041555</v>
+        <v>7041630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1241,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122359201</v>
+        <v>122359117</v>
       </c>
       <c r="B7" t="n">
-        <v>90833</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,26 +1284,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583907</v>
+        <v>583895</v>
       </c>
       <c r="R7" t="n">
-        <v>7041602</v>
+        <v>7041636</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,22 +1373,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122357665</v>
+        <v>122359168</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,6 +1403,11 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1386,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583884</v>
+        <v>583901</v>
       </c>
       <c r="R8" t="n">
-        <v>7041654</v>
+        <v>7041612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,12 +1475,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359168</v>
+        <v>122359142</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,34 +1523,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583901</v>
+        <v>583884</v>
       </c>
       <c r="R9" t="n">
-        <v>7041612</v>
+        <v>7041633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,12 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,22 +1607,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359140</v>
+        <v>122357665</v>
       </c>
       <c r="B10" t="n">
-        <v>55979</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,23 +1635,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1624,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583893</v>
+        <v>583884</v>
       </c>
       <c r="R10" t="n">
-        <v>7041630</v>
+        <v>7041654</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1709,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360157</v>
+        <v>122359314</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583950</v>
+        <v>583896</v>
       </c>
       <c r="R2" t="n">
-        <v>7041511</v>
+        <v>7041555</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359201</v>
+        <v>122359674</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,43 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583907</v>
+        <v>583906</v>
       </c>
       <c r="R3" t="n">
-        <v>7041602</v>
+        <v>7041535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122359314</v>
+        <v>122359142</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583896</v>
+        <v>583884</v>
       </c>
       <c r="R4" t="n">
-        <v>7041555</v>
+        <v>7041633</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359674</v>
+        <v>122359140</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>55983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,34 +1032,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583906</v>
+        <v>583893</v>
       </c>
       <c r="R5" t="n">
-        <v>7041535</v>
+        <v>7041630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359140</v>
+        <v>122360157</v>
       </c>
       <c r="B6" t="n">
-        <v>55983</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,31 +1153,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1196,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583893</v>
+        <v>583950</v>
       </c>
       <c r="R6" t="n">
-        <v>7041630</v>
+        <v>7041511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,7 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122359117</v>
+        <v>122357665</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,16 +1275,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1313,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583895</v>
+        <v>583884</v>
       </c>
       <c r="R7" t="n">
-        <v>7041636</v>
+        <v>7041654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,22 +1369,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122359168</v>
+        <v>122359117</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,16 +1397,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1430,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583901</v>
+        <v>583895</v>
       </c>
       <c r="R8" t="n">
-        <v>7041612</v>
+        <v>7041636</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,22 +1486,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359142</v>
+        <v>122359168</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,34 +1514,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583884</v>
+        <v>583901</v>
       </c>
       <c r="R9" t="n">
-        <v>7041633</v>
+        <v>7041612</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,22 +1608,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122357665</v>
+        <v>122359201</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>90859</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,27 +1636,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583884</v>
+        <v>583907</v>
       </c>
       <c r="R10" t="n">
-        <v>7041654</v>
+        <v>7041602</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,12 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359314</v>
+        <v>122359674</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583896</v>
+        <v>583906</v>
       </c>
       <c r="R2" t="n">
-        <v>7041555</v>
+        <v>7041535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359674</v>
+        <v>122360157</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583906</v>
+        <v>583950</v>
       </c>
       <c r="R3" t="n">
-        <v>7041535</v>
+        <v>7041511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122359142</v>
+        <v>122359201</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>90859</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +925,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583884</v>
+        <v>583907</v>
       </c>
       <c r="R4" t="n">
-        <v>7041633</v>
+        <v>7041602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359140</v>
+        <v>122359117</v>
       </c>
       <c r="B5" t="n">
-        <v>55983</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,28 +1046,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1065,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583893</v>
+        <v>583895</v>
       </c>
       <c r="R5" t="n">
-        <v>7041630</v>
+        <v>7041636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,19 +1135,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122360157</v>
+        <v>122357665</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1173,7 +1183,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583950</v>
+        <v>583884</v>
       </c>
       <c r="R6" t="n">
-        <v>7041511</v>
+        <v>7041654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122357665</v>
+        <v>122359142</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,29 +1285,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
@@ -1307,7 +1312,7 @@
         <v>583884</v>
       </c>
       <c r="R7" t="n">
-        <v>7041654</v>
+        <v>7041633</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,22 +1369,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122359117</v>
+        <v>122359168</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,16 +1397,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583895</v>
+        <v>583901</v>
       </c>
       <c r="R8" t="n">
-        <v>7041636</v>
+        <v>7041612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1491,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359168</v>
+        <v>122359314</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,16 +1519,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1543,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583901</v>
+        <v>583896</v>
       </c>
       <c r="R9" t="n">
-        <v>7041612</v>
+        <v>7041555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,12 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359201</v>
+        <v>122359140</v>
       </c>
       <c r="B10" t="n">
-        <v>90859</v>
+        <v>55983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583907</v>
+        <v>583893</v>
       </c>
       <c r="R10" t="n">
-        <v>7041602</v>
+        <v>7041630</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359674</v>
+        <v>122359140</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>55983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583906</v>
+        <v>583893</v>
       </c>
       <c r="R2" t="n">
-        <v>7041535</v>
+        <v>7041630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360157</v>
+        <v>122359674</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583950</v>
+        <v>583906</v>
       </c>
       <c r="R3" t="n">
-        <v>7041511</v>
+        <v>7041535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122359201</v>
+        <v>122359142</v>
       </c>
       <c r="B4" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,43 +924,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583907</v>
+        <v>583884</v>
       </c>
       <c r="R4" t="n">
-        <v>7041602</v>
+        <v>7041633</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359117</v>
+        <v>122359201</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>90853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,27 +1036,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583895</v>
+        <v>583907</v>
       </c>
       <c r="R5" t="n">
-        <v>7041636</v>
+        <v>7041602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,22 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122357665</v>
+        <v>122359117</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,16 +1157,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1192,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583884</v>
+        <v>583895</v>
       </c>
       <c r="R6" t="n">
-        <v>7041654</v>
+        <v>7041636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1246,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122359142</v>
+        <v>122360157</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,34 +1274,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583884</v>
+        <v>583950</v>
       </c>
       <c r="R7" t="n">
-        <v>7041633</v>
+        <v>7041511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1348,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,19 +1368,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122359168</v>
+        <v>122357665</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1426,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583901</v>
+        <v>583884</v>
       </c>
       <c r="R8" t="n">
-        <v>7041612</v>
+        <v>7041654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1620,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359140</v>
+        <v>122359168</v>
       </c>
       <c r="B10" t="n">
-        <v>55983</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,28 +1635,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583893</v>
+        <v>583901</v>
       </c>
       <c r="R10" t="n">
-        <v>7041630</v>
+        <v>7041612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1709,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359140</v>
+        <v>122359168</v>
       </c>
       <c r="B2" t="n">
-        <v>55983</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583893</v>
+        <v>583901</v>
       </c>
       <c r="R2" t="n">
-        <v>7041630</v>
+        <v>7041612</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359674</v>
+        <v>122359314</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583906</v>
+        <v>583896</v>
       </c>
       <c r="R3" t="n">
-        <v>7041535</v>
+        <v>7041555</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +902,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1020,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359201</v>
+        <v>122357665</v>
       </c>
       <c r="B5" t="n">
-        <v>90853</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,31 +1042,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583907</v>
+        <v>583884</v>
       </c>
       <c r="R5" t="n">
-        <v>7041602</v>
+        <v>7041654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359117</v>
+        <v>122359140</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>55983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,24 +1164,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1186,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583895</v>
+        <v>583893</v>
       </c>
       <c r="R6" t="n">
-        <v>7041636</v>
+        <v>7041630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122360157</v>
+        <v>122359201</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>90853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,27 +1285,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1303,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583950</v>
+        <v>583907</v>
       </c>
       <c r="R7" t="n">
-        <v>7041511</v>
+        <v>7041602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,12 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122357665</v>
+        <v>122359674</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,39 +1406,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583884</v>
+        <v>583906</v>
       </c>
       <c r="R8" t="n">
-        <v>7041654</v>
+        <v>7041535</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,22 +1490,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359314</v>
+        <v>122360157</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583896</v>
+        <v>583950</v>
       </c>
       <c r="R9" t="n">
-        <v>7041555</v>
+        <v>7041511</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1592,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359168</v>
+        <v>122359117</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,16 +1640,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583901</v>
+        <v>583895</v>
       </c>
       <c r="R10" t="n">
-        <v>7041612</v>
+        <v>7041636</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,12 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,12 +1729,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122359168</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359314</v>
+        <v>122359201</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>90854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,27 +813,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583896</v>
+        <v>583907</v>
       </c>
       <c r="R3" t="n">
-        <v>7041555</v>
+        <v>7041602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122359142</v>
+        <v>122357665</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,24 +934,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
@@ -957,7 +966,7 @@
         <v>583884</v>
       </c>
       <c r="R4" t="n">
-        <v>7041633</v>
+        <v>7041654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1028,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122357665</v>
+        <v>122360157</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,7 +1076,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583884</v>
+        <v>583950</v>
       </c>
       <c r="R5" t="n">
-        <v>7041654</v>
+        <v>7041511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359140</v>
+        <v>122359314</v>
       </c>
       <c r="B6" t="n">
-        <v>55983</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,28 +1178,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1197,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583893</v>
+        <v>583896</v>
       </c>
       <c r="R6" t="n">
-        <v>7041630</v>
+        <v>7041555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122359201</v>
+        <v>122359140</v>
       </c>
       <c r="B7" t="n">
-        <v>90853</v>
+        <v>55984</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,31 +1295,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1318,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583907</v>
+        <v>583893</v>
       </c>
       <c r="R7" t="n">
-        <v>7041602</v>
+        <v>7041630</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,7 +1403,7 @@
         <v>122359674</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1502,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122360157</v>
+        <v>122359117</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,16 +1528,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1538,7 +1548,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1547,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583950</v>
+        <v>583895</v>
       </c>
       <c r="R9" t="n">
-        <v>7041511</v>
+        <v>7041636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,12 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,22 +1617,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359117</v>
+        <v>122359142</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,39 +1645,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583895</v>
+        <v>583884</v>
       </c>
       <c r="R10" t="n">
-        <v>7041636</v>
+        <v>7041633</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122359201</v>
+        <v>122360157</v>
       </c>
       <c r="B3" t="n">
-        <v>90854</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,31 +813,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583907</v>
+        <v>583950</v>
       </c>
       <c r="R3" t="n">
-        <v>7041602</v>
+        <v>7041511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122357665</v>
+        <v>122359117</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583884</v>
+        <v>583895</v>
       </c>
       <c r="R4" t="n">
-        <v>7041654</v>
+        <v>7041636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,22 +1024,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122360157</v>
+        <v>122359140</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>55984</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,27 +1052,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583950</v>
+        <v>583893</v>
       </c>
       <c r="R5" t="n">
-        <v>7041511</v>
+        <v>7041630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122359314</v>
+        <v>122357665</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,16 +1173,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1207,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583896</v>
+        <v>583884</v>
       </c>
       <c r="R6" t="n">
-        <v>7041555</v>
+        <v>7041654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1247,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122359140</v>
+        <v>122359201</v>
       </c>
       <c r="B7" t="n">
-        <v>55984</v>
+        <v>90857</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,31 +1295,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583893</v>
+        <v>583907</v>
       </c>
       <c r="R7" t="n">
-        <v>7041630</v>
+        <v>7041602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,7 +1403,7 @@
         <v>122359674</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359117</v>
+        <v>122359314</v>
       </c>
       <c r="B9" t="n">
         <v>57400</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583895</v>
+        <v>583896</v>
       </c>
       <c r="R9" t="n">
-        <v>7041636</v>
+        <v>7041555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,12 +1617,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1632,7 +1632,7 @@
         <v>122359142</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 3923-2025 artfynd.xlsx
+++ b/artfynd/A 3923-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122359168</v>
+        <v>122357665</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583901</v>
+        <v>583884</v>
       </c>
       <c r="R2" t="n">
-        <v>7041612</v>
+        <v>7041654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360157</v>
+        <v>122359201</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,27 +813,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583950</v>
+        <v>583907</v>
       </c>
       <c r="R3" t="n">
-        <v>7041511</v>
+        <v>7041602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1036,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122359140</v>
+        <v>122359314</v>
       </c>
       <c r="B5" t="n">
-        <v>55984</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,28 +1051,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1085,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583893</v>
+        <v>583896</v>
       </c>
       <c r="R5" t="n">
-        <v>7041630</v>
+        <v>7041555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122357665</v>
+        <v>122359168</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1202,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583884</v>
+        <v>583901</v>
       </c>
       <c r="R6" t="n">
-        <v>7041654</v>
+        <v>7041612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,12 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122359201</v>
+        <v>122359140</v>
       </c>
       <c r="B7" t="n">
-        <v>90857</v>
+        <v>55984</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,31 +1290,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1328,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583907</v>
+        <v>583893</v>
       </c>
       <c r="R7" t="n">
-        <v>7041602</v>
+        <v>7041630</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1512,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122359314</v>
+        <v>122359142</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,39 +1523,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583896</v>
+        <v>583884</v>
       </c>
       <c r="R9" t="n">
-        <v>7041555</v>
+        <v>7041633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,22 +1607,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122359142</v>
+        <v>122360157</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,34 +1635,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjällsjöälven, Fjällsjöälven, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583884</v>
+        <v>583950</v>
       </c>
       <c r="R10" t="n">
-        <v>7041633</v>
+        <v>7041511</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1709,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,12 +1729,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
